--- a/UserAccess/AccessTokens.xlsx
+++ b/UserAccess/AccessTokens.xlsx
@@ -8,24 +8,35 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://inforonline-my.sharepoint.com/personal/sriakshitha_thipparapu_infor_com/Documents/Documents/Akshitha/NextGenAIQuiz/UserAccess/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="13" documentId="11_F25DC773A252ABDACC10488739D86E105ADE58F4" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FF87046E-BEAD-4C22-8082-C0F8A1CD77EB}"/>
+  <xr:revisionPtr revIDLastSave="28" documentId="11_F25DC773A252ABDACC10488739D86E105ADE58F4" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8BC30586-D08E-4CA6-BDD2-0F177DFCF458}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
   <si>
     <t>Access_Code</t>
   </si>
@@ -33,22 +44,37 @@
     <t>sriakshitha.thipparapu@infor.com</t>
   </si>
   <si>
-    <t>INF_0001</t>
-  </si>
-  <si>
     <t>mahathi.dasari@infor.com</t>
   </si>
   <si>
-    <t>INF_0002</t>
-  </si>
-  <si>
-    <t>INF_0003</t>
-  </si>
-  <si>
     <t>ajay.battula@infor.com</t>
   </si>
   <si>
     <t xml:space="preserve">Email </t>
+  </si>
+  <si>
+    <t>hammad.hussain@infor.com</t>
+  </si>
+  <si>
+    <t>ritesh.gandhare@infor.com</t>
+  </si>
+  <si>
+    <t>vijaya.marni@infor.com</t>
+  </si>
+  <si>
+    <t>Bharadwaj.Aryasomayajula@infor.com</t>
+  </si>
+  <si>
+    <t>hanumantha.turaga@infor.com</t>
+  </si>
+  <si>
+    <t>imran.khan@infor.com</t>
+  </si>
+  <si>
+    <t>Vidyasagar.Immidisetti@infor.com</t>
+  </si>
+  <si>
+    <t>INF_0010</t>
   </si>
 </sst>
 </file>
@@ -121,7 +147,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top"/>
@@ -134,6 +160,9 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -420,7 +449,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B4"/>
+  <dimension ref="A1:B11"/>
   <sheetFormatPr defaultColWidth="24.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="16384" width="24.1796875" style="1"/>
@@ -428,7 +457,7 @@
   <sheetData>
     <row r="1" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A1" s="2" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>0</v>
@@ -438,30 +467,98 @@
       <c r="A2" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="3" t="s">
-        <v>2</v>
+      <c r="B2" s="3" t="str">
+        <f t="shared" ref="B2:B11" si="0">"INF_000" &amp; TEXT(ROW() - ROW($B$2) + 1, "[$-en-IN]0;-0")</f>
+        <v>INF_0001</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A3" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>4</v>
+        <v>2</v>
+      </c>
+      <c r="B3" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>INF_0002</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>INF_0003</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A5" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>INF_0004</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A6" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="3" t="s">
-        <v>5</v>
+      <c r="B6" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>INF_0005</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A7" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="B7" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>INF_0006</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A8" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B8" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>INF_0007</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A9" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B9" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>INF_0008</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A10" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B10" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>INF_0009</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A11" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>12</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="A3" r:id="rId1" xr:uid="{3771A3EA-E2D2-4D77-BA85-FC9A9128B5D8}"/>
     <hyperlink ref="A4" r:id="rId2" xr:uid="{6C4C317E-E568-492C-B1A9-B584C5CDFC3E}"/>
+    <hyperlink ref="A5" r:id="rId3" xr:uid="{63815153-4E39-4B81-A411-4D06657FC061}"/>
+    <hyperlink ref="A6" r:id="rId4" xr:uid="{AFF0ABCE-8276-4B57-A07F-8EA151681A0C}"/>
+    <hyperlink ref="A7" r:id="rId5" xr:uid="{1A73CBB5-6891-4CC7-AF9B-6AEEC023F1AA}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
